--- a/docs/2/db-design/Учебный_план_Основы_проектирования_баз_данных.xlsx
+++ b/docs/2/db-design/Учебный_план_Основы_проектирования_баз_данных.xlsx
@@ -174,7 +174,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
@@ -195,12 +195,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Данные, информация и базы данных»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете, чем данные отличаются от информации, зачем нужна база данных и какие уровни представления проходит предметная область до таблиц.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Данные, информация и базы данных</t>
+          <t xml:space="preserve">файловое хранение, СУБД, предметная область, уровни представления, избыточность, целостность</t>
         </is>
       </c>
     </row>
@@ -225,12 +225,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Выделение сущностей и связей»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Разбираете предметную область учебной ИС, выписываете сущности и связи между ними и сдаёте перечень с обоснованием, почему объект стал сущностью.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Выделение сущностей и связей</t>
+          <t xml:space="preserve">предметная область, сущность, экземпляр, связь, участник связи</t>
         </is>
       </c>
     </row>
@@ -255,12 +255,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Реляционная модель»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете отношение как таблицу: кортежи, атрибуты, домены и степень отношения, и проверяете, когда набор данных действительно является отношением.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Реляционная модель</t>
+          <t xml:space="preserve">отношение, кортеж, атрибут, домен, степень, кардинальность</t>
         </is>
       </c>
     </row>
@@ -285,12 +285,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «ER-диаграмма в draw.io»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Строите ER-диаграмму учебной ИС в draw.io по нотации «воронья лапка» и сдаёте PDF со всеми сущностями, атрибутами и подписанной кратностью связей.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ER-диаграмма в draw.io</t>
+          <t xml:space="preserve">draw.io, нотация вороньей лапки, кратность, атрибут, экспорт в PDF</t>
         </is>
       </c>
     </row>
@@ -315,16 +315,16 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Сущности и атрибуты»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете, как отличить сущность от атрибута, какие бывают атрибуты и почему составной атрибут часто становится отдельной таблицей.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сущности и атрибуты</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="45" customHeight="1">
+          <t xml:space="preserve">сущность, атрибут, составной атрибут, многозначный атрибут, ключевой атрибут</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
@@ -345,12 +345,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Нормализация до 3НФ»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Приводите широкую таблицу к 3НФ за три шага, фиксируете каждый переход и сдаёте набор таблиц с обоснованием, что аномалий вставки и удаления больше нет.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Нормализация до 3НФ</t>
+          <t xml:space="preserve">1НФ, 2НФ, 3НФ, повторяющаяся группа, частичная зависимость, транзитивная зависимость</t>
         </is>
       </c>
     </row>
@@ -375,12 +375,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Связи и кратность»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете, как читать и записывать связи 1:1, 1:N и M:N, где ставится внешний ключ и почему связь многие-ко-многим требует отдельной таблицы.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Связи и кратность</t>
+          <t xml:space="preserve">кратность, 1:1, 1:N, M:N, внешний ключ, таблица связи</t>
         </is>
       </c>
     </row>
@@ -405,16 +405,16 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «ER-модель»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Собираете сущности и связи в целостную ER-модель, проверяете её на лишние дубли и готовите основу для перевода в таблицы.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ER-модель</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
+          <t xml:space="preserve">ER-модель, концептуальная модель, связь, атрибут, проверка полноты</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">9-10</t>
@@ -435,16 +435,16 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Создание БД в sqliteonline.com; Ограничения и ключи.</t>
+          <t xml:space="preserve">Создаёте базу учебной ИС в sqliteonline.com: таблицы с первичными и внешними ключами, ограничения NOT NULL, UNIQUE и CHECK, и сдаёте SQL-скрипт, который выполняется без ошибок.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Создание БД в sqliteonline.com, Ограничения и ключи</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
+          <t xml:space="preserve">sqliteonline.com, CREATE TABLE, первичный ключ, внешний ключ, NOT NULL, CHECK</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
@@ -465,16 +465,16 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Ключи: первичный, внешний, альтернативный»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете, чем первичный ключ отличается от альтернативного и внешнего, и как выбрать ключ, который не придётся менять через год.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ключи: первичный, внешний, альтернативный</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1">
+          <t xml:space="preserve">первичный ключ, альтернативный ключ, внешний ключ, суррогатный ключ, естественный ключ, составной ключ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
@@ -495,16 +495,16 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Целостность данных»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете виды целостности: сущностную, ссылочную и доменную, и какие ограничения СУБД защищают каждую из них.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Целостность данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
+          <t xml:space="preserve">сущностная целостность, ссылочная целостность, доменная целостность, каскадное удаление, ограничение</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">13-14</t>
@@ -525,12 +525,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Запросы SELECT; JOIN и агрегация.</t>
+          <t xml:space="preserve">Пишете набор SELECT-запросов к базе учебной ИС: выборка с условием, соединение двух и трёх таблиц, группировка с COUNT и SUM, и сдаёте SQL-файл с комментариями к каждому запросу.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Запросы SELECT, JOIN и агрегация</t>
+          <t xml:space="preserve">SELECT, WHERE, соединение таблиц, GROUP BY, COUNT, SUM</t>
         </is>
       </c>
     </row>
@@ -555,12 +555,12 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Нормализация: 1НФ»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете первое нормальное условие: атомарные значения в каждой ячейке и почему список предметов в одном поле ломает запросы.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Нормализация: 1НФ</t>
+          <t xml:space="preserve">1НФ, атомарное значение, повторяющаяся группа, многозначный атрибут, первичный ключ</t>
         </is>
       </c>
     </row>
@@ -585,16 +585,16 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Импорт JSON»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Загружаете данные из JSON в таблицы учебной ИС, проверяете типы и полноту переноса и сдаёте скрипт импорта с отчётом о числе строк до и после.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Импорт JSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
+          <t xml:space="preserve">json-файл, сверка строк, типы данных, sqliteonline.com, скрипт загрузки</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
@@ -615,16 +615,16 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Нормализация: 2НФ»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете второе нормальное условие: полную зависимость неключевых атрибутов от всего составного ключа и то, как частичная зависимость портит данные.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Нормализация: 2НФ</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
+          <t xml:space="preserve">2НФ, составной ключ, частичная зависимость, неключевой атрибут, декомпозиция</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
@@ -645,16 +645,16 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Нормализация: 3НФ»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете третье нормальное условие: транзитивную зависимость, когда неключевой атрибут зависит от другого неключевого, и учитесь разрывать такую цепочку.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Нормализация: 3НФ</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="45" customHeight="1">
+          <t xml:space="preserve">3НФ, транзитивная зависимость, неключевой атрибут, справочник, декомпозиция, потеря связи</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">19-20</t>
@@ -675,12 +675,12 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Индексы и транзакции; Разграничение доступа.</t>
+          <t xml:space="preserve">Сравниваете время запроса до и после создания индекса, проводите транзакцию с откатом и выдаёте роли разным пользователям, сдавая SQL-скрипт и замеры.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Индексы и транзакции, Разграничение доступа</t>
+          <t xml:space="preserve">B-дерево, план запроса, транзакция, COMMIT, ROLLBACK, GRANT</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Нормальная форма Бойса-Кодда»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете, когда 3НФ недостаточно и нормальная форма Бойса-Кодда требует, чтобы каждый детерминант был потенциальным ключом.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Нормальная форма Бойса-Кодда</t>
+          <t xml:space="preserve">BCNF, детерминант, потенциальный ключ, функциональная зависимость, аномалия</t>
         </is>
       </c>
     </row>
@@ -735,12 +735,12 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Итоговая БД для учебной ИС»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Собираете итоговую базу учебной ИС: ER-модель, таблицы с ограничениями, данные и типовые запросы, и сдаёте комплект из PDF-диаграммы и SQL-скрипта.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Итоговая БД для учебной ИС</t>
+          <t xml:space="preserve">учебная ИС, схема БД, ER-модель, типовой запрос, комплект поставки</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Преобразование ER в таблицы»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Переводите ER-модель в набор таблиц: сущность становится таблицей, связь M:N отдельной таблицей, а кратность задаёт место внешнего ключа.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Преобразование ER в таблицы</t>
+          <t xml:space="preserve">перенос ключа, таблица связи, внешний ключ, первичный ключ, кратность</t>
         </is>
       </c>
     </row>
@@ -795,12 +795,12 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Типы данных SQL»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете основные типы SQL: целые, вещественные, текст, дата и время, и как выбор типа влияет на проверки и размер базы.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Типы данных SQL</t>
+          <t xml:space="preserve">INTEGER, REAL, TEXT, DATE, тип данных, приведение типов</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Создание таблиц и ограничений»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете синтаксис CREATE TABLE: столбцы, типы, значения по умолчанию, первичные и внешние ключи и порядок создания связанных таблиц.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Создание таблиц и ограничений</t>
+          <t xml:space="preserve">CREATE TABLE, DEFAULT, NOT NULL, FOREIGN KEY, PRIMARY KEY, порядок создания</t>
         </is>
       </c>
     </row>
@@ -855,12 +855,12 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Изменение структуры таблиц»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете ALTER TABLE: добавление и удаление столбца, переименование, смену ограничений и чем ограничен SQLite при изменении готовой таблицы.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Изменение структуры таблиц</t>
+          <t xml:space="preserve">ALTER TABLE, ADD COLUMN, RENAME, DROP COLUMN, ограничения SQLite</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Добавление, обновление и удаление данных»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете INSERT, UPDATE и DELETE: как не задеть лишние строки, зачем нужен WHERE и что происходит при нарушении внешнего ключа.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Добавление, обновление и удаление данных</t>
+          <t xml:space="preserve">INSERT, UPDATE, DELETE, WHERE, внешний ключ, откат</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Выборка данных»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете структуру SELECT: список столбцов, псевдонимы, DISTINCT, вычисляемые поля и порядок выполнения частей запроса.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Выборка данных</t>
+          <t xml:space="preserve">SELECT, псевдоним, DISTINCT, вычисляемый столбец, порядок выполнения</t>
         </is>
       </c>
     </row>
@@ -945,16 +945,16 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Фильтрация и сортировка»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете WHERE, логические операторы, LIKE, BETWEEN, IN и ORDER BY, а также разницу между фильтрацией строк и сортировкой результата.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Фильтрация и сортировка</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
+          <t xml:space="preserve">WHERE, AND, OR, LIKE, BETWEEN, ORDER BY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="45" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
@@ -975,12 +975,12 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «JOIN»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете виды соединений: INNER, LEFT, RIGHT и FULL, что происходит со строками без пары и как читать результат соединения трёх таблиц.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOIN</t>
+          <t xml:space="preserve">INNER JOIN, LEFT JOIN, RIGHT JOIN, FULL JOIN, ON, соединение таблиц</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Агрегация и группировка»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете COUNT, SUM, AVG, MIN и MAX вместе с GROUP BY и HAVING: как считать итоги по группам и фильтровать уже посчитанные значения.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Агрегация и группировка</t>
+          <t xml:space="preserve">COUNT, SUM, AVG, GROUP BY, HAVING, агрегатная функция</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Подзапросы»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете подзапросы в WHERE, FROM и SELECT: когда нужен скалярный результат, когда список значений и чем подзапрос отличается от JOIN.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Подзапросы</t>
+          <t xml:space="preserve">подзапрос, скалярный подзапрос, IN, EXISTS, производная таблица</t>
         </is>
       </c>
     </row>
@@ -1065,16 +1065,16 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Представления»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете представления как сохранённый запрос: зачем они нужны, как скрывают структуру таблиц и когда представление нельзя обновлять.</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Представления</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
+          <t xml:space="preserve">CREATE VIEW, представление, сохранённый запрос, обновляемость, права доступа</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="45" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">34</t>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Индексы»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете, как индекс ускоряет поиск, из чего он состоит и почему лишние индексы замедляют вставку и обновление.</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Индексы</t>
+          <t xml:space="preserve">B-дерево, ключ поиска, план запроса, уникальность, стоимость обновления</t>
         </is>
       </c>
     </row>
@@ -1125,16 +1125,16 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Транзакции»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете транзакцию и свойства ACID: как COMMIT и ROLLBACK защищают данные и что происходит при сбое посреди операции.</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Транзакции</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="45" customHeight="1">
+          <t xml:space="preserve">транзакция, ACID, COMMIT, ROLLBACK, блокировка, сбой</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">36</t>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Импорт и экспорт JSON/CSV»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете форматы JSON и CSV, сопоставление полей со столбцами и типичные ошибки кодировки и разделителей при переносе данных.</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Импорт и экспорт JSON/CSV</t>
+          <t xml:space="preserve">кодировка, разделитель, сопоставление полей, схема файла, потеря строк, заголовок столбцов</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Разграничение доступа»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Разбираете роли и права в базе: что дают SELECT, INSERT и DELETE, зачем нужен минимальный набор прав и как проверить выданные разрешения.</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разграничение доступа</t>
+          <t xml:space="preserve">роль, GRANT, REVOKE, минимальные права, пользователь БД</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Проектирование БД для ИС»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Собираете полный цикл проектирования: от требований и ER-модели до нормализации, ограничений и проверки запросами на реальных данных.</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проектирование БД для ИС</t>
+          <t xml:space="preserve">требования, ER-модель, нормализация, ограничения, проверка запросами</t>
         </is>
       </c>
     </row>

--- a/docs/2/db-design/Учебный_план_Основы_проектирования_баз_данных.xlsx
+++ b/docs/2/db-design/Учебный_план_Основы_проектирования_баз_данных.xlsx
@@ -160,7 +160,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Минуты</t>
+          <t xml:space="preserve">Часы</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -191,7 +191,7 @@
         </is>
       </c>
       <c r="D6" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -221,7 +221,7 @@
         </is>
       </c>
       <c r="D7" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -251,7 +251,7 @@
         </is>
       </c>
       <c r="D8" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -281,7 +281,7 @@
         </is>
       </c>
       <c r="D9" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -311,7 +311,7 @@
         </is>
       </c>
       <c r="D10" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -341,7 +341,7 @@
         </is>
       </c>
       <c r="D11" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -371,7 +371,7 @@
         </is>
       </c>
       <c r="D12" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="D13" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -431,7 +431,7 @@
         </is>
       </c>
       <c r="D14" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="D15" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="D16" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="D17" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="D18" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D19" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D20" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="D21" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D22" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="D23" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="D24" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="D25" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="D26" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="D27" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D28" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="D29" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="D31" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="D32" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="D33" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="D34" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="D35" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D36" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="D37" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D38" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="D39" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="D40" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="D41" s="6">
-        <v>3420</v>
+        <v>76</v>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>

--- a/docs/2/db-design/Учебный_план_Основы_проектирования_баз_данных.xlsx
+++ b/docs/2/db-design/Учебный_план_Основы_проектирования_баз_данных.xlsx
@@ -212,12 +212,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 1. Выделение сущностей и связей</t>
+          <t xml:space="preserve">Лекция 2. Реляционная модель</t>
         </is>
       </c>
       <c r="D7" s="6">
@@ -225,12 +225,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете предметную область учебной ИС, выписываете сущности и связи между ними и сдаёте перечень с обоснованием, почему объект стал сущностью.</t>
+          <t xml:space="preserve">Разбираете отношение как таблицу: кортежи, атрибуты, домены и степень отношения, и проверяете, когда набор данных действительно является отношением.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">предметная область, сущность, экземпляр, связь, участник связи</t>
+          <t xml:space="preserve">отношение, кортеж, атрибут, домен, степень, кардинальность</t>
         </is>
       </c>
     </row>
@@ -247,7 +247,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 2. Реляционная модель</t>
+          <t xml:space="preserve">Лекция 3. Сущности и атрибуты</t>
         </is>
       </c>
       <c r="D8" s="6">
@@ -255,12 +255,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете отношение как таблицу: кортежи, атрибуты, домены и степень отношения, и проверяете, когда набор данных действительно является отношением.</t>
+          <t xml:space="preserve">Разбираете, как отличить сущность от атрибута, какие бывают атрибуты и почему составной атрибут часто становится отдельной таблицей.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">отношение, кортеж, атрибут, домен, степень, кардинальность</t>
+          <t xml:space="preserve">сущность, атрибут, составной атрибут, многозначный атрибут, ключевой атрибут</t>
         </is>
       </c>
     </row>
@@ -272,12 +272,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 2. ER-диаграмма в draw.io</t>
+          <t xml:space="preserve">Лекция 4. Связи и кратность</t>
         </is>
       </c>
       <c r="D9" s="6">
@@ -285,12 +285,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Строите ER-диаграмму учебной ИС в draw.io по нотации «воронья лапка» и сдаёте PDF со всеми сущностями, атрибутами и подписанной кратностью связей.</t>
+          <t xml:space="preserve">Разбираете, как читать и записывать связи 1:1, 1:N и M:N, где ставится внешний ключ и почему связь многие-ко-многим требует отдельной таблицы.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">draw.io, нотация вороньей лапки, кратность, атрибут, экспорт в PDF</t>
+          <t xml:space="preserve">кратность, 1:1, 1:N, M:N, внешний ключ, таблица связи</t>
         </is>
       </c>
     </row>
@@ -302,12 +302,12 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 3. Сущности и атрибуты</t>
+          <t xml:space="preserve">Практика 1. Выделение сущностей и связей</t>
         </is>
       </c>
       <c r="D10" s="6">
@@ -315,16 +315,16 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете, как отличить сущность от атрибута, какие бывают атрибуты и почему составной атрибут часто становится отдельной таблицей.</t>
+          <t xml:space="preserve">Разбираете предметную область учебной ИС, выписываете сущности и связи между ними и сдаёте перечень с обоснованием, почему объект стал сущностью.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">сущность, атрибут, составной атрибут, многозначный атрибут, ключевой атрибут</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
+          <t xml:space="preserve">предметная область, сущность, экземпляр, связь, участник связи</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
@@ -332,12 +332,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 3. Нормализация до 3НФ</t>
+          <t xml:space="preserve">Лекция 5. ER-модель</t>
         </is>
       </c>
       <c r="D11" s="6">
@@ -345,12 +345,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Приводите широкую таблицу к 3НФ за три шага, фиксируете каждый переход и сдаёте набор таблиц с обоснованием, что аномалий вставки и удаления больше нет.</t>
+          <t xml:space="preserve">Собираете сущности и связи в целостную ER-модель, проверяете её на лишние дубли и готовите основу для перевода в таблицы.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1НФ, 2НФ, 3НФ, повторяющаяся группа, частичная зависимость, транзитивная зависимость</t>
+          <t xml:space="preserve">ER-модель, концептуальная модель, связь, атрибут, проверка полноты</t>
         </is>
       </c>
     </row>
@@ -362,12 +362,12 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 4. Связи и кратность</t>
+          <t xml:space="preserve">Практика 2. ER-диаграмма в draw.io</t>
         </is>
       </c>
       <c r="D12" s="6">
@@ -375,16 +375,16 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете, как читать и записывать связи 1:1, 1:N и M:N, где ставится внешний ключ и почему связь многие-ко-многим требует отдельной таблицы.</t>
+          <t xml:space="preserve">Строите ER-диаграмму учебной ИС в draw.io по нотации «воронья лапка» и сдаёте PDF со всеми сущностями, атрибутами и подписанной кратностью связей.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">кратность, 1:1, 1:N, M:N, внешний ключ, таблица связи</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
+          <t xml:space="preserve">draw.io, нотация вороньей лапки, кратность, атрибут, экспорт в PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
@@ -397,7 +397,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 5. ER-модель</t>
+          <t xml:space="preserve">Лекция 6. Ключи: первичный, внешний, альтернативный</t>
         </is>
       </c>
       <c r="D13" s="6">
@@ -405,49 +405,49 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Собираете сущности и связи в целостную ER-модель, проверяете её на лишние дубли и готовите основу для перевода в таблицы.</t>
+          <t xml:space="preserve">Разбираете, чем первичный ключ отличается от альтернативного и внешнего, и как выбрать ключ, который не придётся менять через год.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ER-модель, концептуальная модель, связь, атрибут, проверка полноты</t>
+          <t xml:space="preserve">первичный ключ, альтернативный ключ, внешний ключ, суррогатный ключ, естественный ключ, составной ключ</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9-10</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 4. Создание БД в sqliteonline.com; Ограничения и ключи</t>
+          <t xml:space="preserve">Лекция 7. Целостность данных</t>
         </is>
       </c>
       <c r="D14" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Создаёте базу учебной ИС в sqliteonline.com: таблицы с первичными и внешними ключами, ограничения NOT NULL, UNIQUE и CHECK, и сдаёте SQL-скрипт, который выполняется без ошибок.</t>
+          <t xml:space="preserve">Разбираете виды целостности: сущностную, ссылочную и доменную, и какие ограничения СУБД защищают каждую из них.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">sqliteonline.com, CREATE TABLE, первичный ключ, внешний ключ, NOT NULL, CHECK</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
+          <t xml:space="preserve">сущностная целостность, ссылочная целостность, доменная целостность, каскадное удаление, ограничение</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -457,7 +457,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 6. Ключи: первичный, внешний, альтернативный</t>
+          <t xml:space="preserve">Лекция 8. Нормализация: 1НФ</t>
         </is>
       </c>
       <c r="D15" s="6">
@@ -465,19 +465,19 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете, чем первичный ключ отличается от альтернативного и внешнего, и как выбрать ключ, который не придётся менять через год.</t>
+          <t xml:space="preserve">Разбираете первое нормальное условие: атомарные значения в каждой ячейке и почему список предметов в одном поле ломает запросы.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">первичный ключ, альтернативный ключ, внешний ключ, суррогатный ключ, естественный ключ, составной ключ</t>
+          <t xml:space="preserve">1НФ, атомарное значение, повторяющаяся группа, многозначный атрибут, первичный ключ</t>
         </is>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 7. Целостность данных</t>
+          <t xml:space="preserve">Лекция 9. Нормализация: 2НФ</t>
         </is>
       </c>
       <c r="D16" s="6">
@@ -495,59 +495,59 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете виды целостности: сущностную, ссылочную и доменную, и какие ограничения СУБД защищают каждую из них.</t>
+          <t xml:space="preserve">Разбираете второе нормальное условие: полную зависимость неключевых атрибутов от всего составного ключа и то, как частичная зависимость портит данные.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">сущностная целостность, ссылочная целостность, доменная целостность, каскадное удаление, ограничение</t>
+          <t xml:space="preserve">2НФ, составной ключ, частичная зависимость, неключевой атрибут, декомпозиция</t>
         </is>
       </c>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">13-14</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 10. Нормализация: 3НФ</t>
+        </is>
+      </c>
+      <c r="D17" s="6">
+        <v>2</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Разбираете третье нормальное условие: транзитивную зависимость, когда неключевой атрибут зависит от другого неключевого, и учитесь разрывать такую цепочку.</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3НФ, транзитивная зависимость, неключевой атрибут, справочник, декомпозиция, потеря связи</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Практика</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика 5. Запросы SELECT; JOIN и агрегация</t>
-        </is>
-      </c>
-      <c r="D17" s="6">
-        <v>4</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Пишете набор SELECT-запросов к базе учебной ИС: выборка с условием, соединение двух и трёх таблиц, группировка с COUNT и SUM, и сдаёте SQL-файл с комментариями к каждому запросу.</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SELECT, WHERE, соединение таблиц, GROUP BY, COUNT, SUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="45" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 8. Нормализация: 1НФ</t>
+          <t xml:space="preserve">Практика 3. Нормализация до 3НФ</t>
         </is>
       </c>
       <c r="D18" s="6">
@@ -555,179 +555,179 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете первое нормальное условие: атомарные значения в каждой ячейке и почему список предметов в одном поле ломает запросы.</t>
+          <t xml:space="preserve">Приводите широкую таблицу к 3НФ за три шага, фиксируете каждый переход и сдаёте набор таблиц с обоснованием, что аномалий вставки и удаления больше нет.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1НФ, атомарное значение, повторяющаяся группа, многозначный атрибут, первичный ключ</t>
+          <t xml:space="preserve">1НФ, 2НФ, 3НФ, повторяющаяся группа, частичная зависимость, транзитивная зависимость</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 11. Нормальная форма Бойса-Кодда</t>
+        </is>
+      </c>
+      <c r="D19" s="6">
+        <v>2</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Разбираете, когда 3НФ недостаточно и нормальная форма Бойса-Кодда требует, чтобы каждый детерминант был потенциальным ключом.</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCNF, детерминант, потенциальный ключ, функциональная зависимость, аномалия</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 12. Преобразование ER в таблицы</t>
+        </is>
+      </c>
+      <c r="D20" s="6">
+        <v>2</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Переводите ER-модель в набор таблиц: сущность становится таблицей, связь M:N отдельной таблицей, а кратность задаёт место внешнего ключа.</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">перенос ключа, таблица связи, внешний ключ, первичный ключ, кратность</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 13. Типы данных SQL</t>
+        </is>
+      </c>
+      <c r="D21" s="6">
+        <v>2</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Разбираете основные типы SQL: целые, вещественные, текст, дата и время, и как выбор типа влияет на проверки и размер базы.</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INTEGER, REAL, TEXT, DATE, тип данных, приведение типов</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 14. Создание таблиц и ограничений</t>
+        </is>
+      </c>
+      <c r="D22" s="6">
+        <v>2</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Разбираете синтаксис CREATE TABLE: столбцы, типы, значения по умолчанию, первичные и внешние ключи и порядок создания связанных таблиц.</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CREATE TABLE, DEFAULT, NOT NULL, FOREIGN KEY, PRIMARY KEY, порядок создания</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-19</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Практика</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика 6. Импорт JSON</t>
-        </is>
-      </c>
-      <c r="D19" s="6">
-        <v>2</v>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Загружаете данные из JSON в таблицы учебной ИС, проверяете типы и полноту переноса и сдаёте скрипт импорта с отчётом о числе строк до и после.</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">json-файл, сверка строк, типы данных, sqliteonline.com, скрипт загрузки</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 9. Нормализация: 2НФ</t>
-        </is>
-      </c>
-      <c r="D20" s="6">
-        <v>2</v>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Разбираете второе нормальное условие: полную зависимость неключевых атрибутов от всего составного ключа и то, как частичная зависимость портит данные.</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2НФ, составной ключ, частичная зависимость, неключевой атрибут, декомпозиция</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 10. Нормализация: 3НФ</t>
-        </is>
-      </c>
-      <c r="D21" s="6">
-        <v>2</v>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Разбираете третье нормальное условие: транзитивную зависимость, когда неключевой атрибут зависит от другого неключевого, и учитесь разрывать такую цепочку.</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3НФ, транзитивная зависимость, неключевой атрибут, справочник, декомпозиция, потеря связи</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19-20</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика 7. Индексы и транзакции; Разграничение доступа</t>
-        </is>
-      </c>
-      <c r="D22" s="6">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика 4. Создание БД в sqliteonline.com; Ограничения и ключи</t>
+        </is>
+      </c>
+      <c r="D23" s="6">
         <v>4</v>
       </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Сравниваете время запроса до и после создания индекса, проводите транзакцию с откатом и выдаёте роли разным пользователям, сдавая SQL-скрипт и замеры.</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B-дерево, план запроса, транзакция, COMMIT, ROLLBACK, GRANT</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 11. Нормальная форма Бойса-Кодда</t>
-        </is>
-      </c>
-      <c r="D23" s="6">
-        <v>2</v>
-      </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете, когда 3НФ недостаточно и нормальная форма Бойса-Кодда требует, чтобы каждый детерминант был потенциальным ключом.</t>
+          <t xml:space="preserve">Создаёте базу учебной ИС в sqliteonline.com: таблицы с первичными и внешними ключами, ограничения NOT NULL, UNIQUE и CHECK, и сдаёте SQL-скрипт, который выполняется без ошибок.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">BCNF, детерминант, потенциальный ключ, функциональная зависимость, аномалия</t>
+          <t xml:space="preserve">sqliteonline.com, CREATE TABLE, первичный ключ, внешний ключ, NOT NULL, CHECK</t>
         </is>
       </c>
     </row>
     <row r="24" ht="45" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 8. Итоговая БД для учебной ИС</t>
+          <t xml:space="preserve">Лекция 15. Изменение структуры таблиц</t>
         </is>
       </c>
       <c r="D24" s="6">
@@ -735,19 +735,19 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Собираете итоговую базу учебной ИС: ER-модель, таблицы с ограничениями, данные и типовые запросы, и сдаёте комплект из PDF-диаграммы и SQL-скрипта.</t>
+          <t xml:space="preserve">Разбираете ALTER TABLE: добавление и удаление столбца, переименование, смену ограничений и чем ограничен SQLite при изменении готовой таблицы.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">учебная ИС, схема БД, ER-модель, типовой запрос, комплект поставки</t>
+          <t xml:space="preserve">ALTER TABLE, ADD COLUMN, RENAME, DROP COLUMN, ограничения SQLite</t>
         </is>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 12. Преобразование ER в таблицы</t>
+          <t xml:space="preserve">Лекция 16. Добавление, обновление и удаление данных</t>
         </is>
       </c>
       <c r="D25" s="6">
@@ -765,19 +765,19 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Переводите ER-модель в набор таблиц: сущность становится таблицей, связь M:N отдельной таблицей, а кратность задаёт место внешнего ключа.</t>
+          <t xml:space="preserve">Разбираете INSERT, UPDATE и DELETE: как не задеть лишние строки, зачем нужен WHERE и что происходит при нарушении внешнего ключа.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">перенос ключа, таблица связи, внешний ключ, первичный ключ, кратность</t>
+          <t xml:space="preserve">INSERT, UPDATE, DELETE, WHERE, внешний ключ, откат</t>
         </is>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 13. Типы данных SQL</t>
+          <t xml:space="preserve">Лекция 17. Выборка данных</t>
         </is>
       </c>
       <c r="D26" s="6">
@@ -795,19 +795,19 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете основные типы SQL: целые, вещественные, текст, дата и время, и как выбор типа влияет на проверки и размер базы.</t>
+          <t xml:space="preserve">Разбираете структуру SELECT: список столбцов, псевдонимы, DISTINCT, вычисляемые поля и порядок выполнения частей запроса.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">INTEGER, REAL, TEXT, DATE, тип данных, приведение типов</t>
+          <t xml:space="preserve">SELECT, псевдоним, DISTINCT, вычисляемый столбец, порядок выполнения</t>
         </is>
       </c>
     </row>
     <row r="27" ht="45" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 14. Создание таблиц и ограничений</t>
+          <t xml:space="preserve">Лекция 18. Фильтрация и сортировка</t>
         </is>
       </c>
       <c r="D27" s="6">
@@ -825,19 +825,19 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете синтаксис CREATE TABLE: столбцы, типы, значения по умолчанию, первичные и внешние ключи и порядок создания связанных таблиц.</t>
+          <t xml:space="preserve">Разбираете WHERE, логические операторы, LIKE, BETWEEN, IN и ORDER BY, а также разницу между фильтрацией строк и сортировкой результата.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREATE TABLE, DEFAULT, NOT NULL, FOREIGN KEY, PRIMARY KEY, порядок создания</t>
+          <t xml:space="preserve">WHERE, AND, OR, LIKE, BETWEEN, ORDER BY</t>
         </is>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 15. Изменение структуры таблиц</t>
+          <t xml:space="preserve">Лекция 19. JOIN</t>
         </is>
       </c>
       <c r="D28" s="6">
@@ -855,19 +855,19 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете ALTER TABLE: добавление и удаление столбца, переименование, смену ограничений и чем ограничен SQLite при изменении готовой таблицы.</t>
+          <t xml:space="preserve">Разбираете виды соединений: INNER, LEFT, RIGHT и FULL, что происходит со строками без пары и как читать результат соединения трёх таблиц.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALTER TABLE, ADD COLUMN, RENAME, DROP COLUMN, ограничения SQLite</t>
+          <t xml:space="preserve">INNER JOIN, LEFT JOIN, RIGHT JOIN, FULL JOIN, ON, соединение таблиц</t>
         </is>
       </c>
     </row>
     <row r="29" ht="45" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 16. Добавление, обновление и удаление данных</t>
+          <t xml:space="preserve">Лекция 20. Агрегация и группировка</t>
         </is>
       </c>
       <c r="D29" s="6">
@@ -885,49 +885,49 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете INSERT, UPDATE и DELETE: как не задеть лишние строки, зачем нужен WHERE и что происходит при нарушении внешнего ключа.</t>
+          <t xml:space="preserve">Разбираете COUNT, SUM, AVG, MIN и MAX вместе с GROUP BY и HAVING: как считать итоги по группам и фильтровать уже посчитанные значения.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">INSERT, UPDATE, DELETE, WHERE, внешний ключ, откат</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="45" customHeight="1">
+          <t xml:space="preserve">COUNT, SUM, AVG, GROUP BY, HAVING, агрегатная функция</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">26-27</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 17. Выборка данных</t>
+          <t xml:space="preserve">Практика 5. Запросы SELECT; JOIN и агрегация</t>
         </is>
       </c>
       <c r="D30" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете структуру SELECT: список столбцов, псевдонимы, DISTINCT, вычисляемые поля и порядок выполнения частей запроса.</t>
+          <t xml:space="preserve">Пишете набор SELECT-запросов к базе учебной ИС: выборка с условием, соединение двух и трёх таблиц, группировка с COUNT и SUM, и сдаёте SQL-файл с комментариями к каждому запросу.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SELECT, псевдоним, DISTINCT, вычисляемый столбец, порядок выполнения</t>
+          <t xml:space="preserve">SELECT, WHERE, соединение таблиц, GROUP BY, COUNT, SUM</t>
         </is>
       </c>
     </row>
     <row r="31" ht="45" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 18. Фильтрация и сортировка</t>
+          <t xml:space="preserve">Лекция 21. Подзапросы</t>
         </is>
       </c>
       <c r="D31" s="6">
@@ -945,19 +945,19 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете WHERE, логические операторы, LIKE, BETWEEN, IN и ORDER BY, а также разницу между фильтрацией строк и сортировкой результата.</t>
+          <t xml:space="preserve">Разбираете подзапросы в WHERE, FROM и SELECT: когда нужен скалярный результат, когда список значений и чем подзапрос отличается от JOIN.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">WHERE, AND, OR, LIKE, BETWEEN, ORDER BY</t>
+          <t xml:space="preserve">подзапрос, скалярный подзапрос, IN, EXISTS, производная таблица</t>
         </is>
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 19. JOIN</t>
+          <t xml:space="preserve">Лекция 22. Представления</t>
         </is>
       </c>
       <c r="D32" s="6">
@@ -975,19 +975,19 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете виды соединений: INNER, LEFT, RIGHT и FULL, что происходит со строками без пары и как читать результат соединения трёх таблиц.</t>
+          <t xml:space="preserve">Разбираете представления как сохранённый запрос: зачем они нужны, как скрывают структуру таблиц и когда представление нельзя обновлять.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">INNER JOIN, LEFT JOIN, RIGHT JOIN, FULL JOIN, ON, соединение таблиц</t>
+          <t xml:space="preserve">CREATE VIEW, представление, сохранённый запрос, обновляемость, права доступа</t>
         </is>
       </c>
     </row>
     <row r="33" ht="45" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 20. Агрегация и группировка</t>
+          <t xml:space="preserve">Лекция 23. Индексы</t>
         </is>
       </c>
       <c r="D33" s="6">
@@ -1005,51 +1005,51 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете COUNT, SUM, AVG, MIN и MAX вместе с GROUP BY и HAVING: как считать итоги по группам и фильтровать уже посчитанные значения.</t>
+          <t xml:space="preserve">Разбираете, как индекс ускоряет поиск, из чего он состоит и почему лишние индексы замедляют вставку и обновление.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">COUNT, SUM, AVG, GROUP BY, HAVING, агрегатная функция</t>
+          <t xml:space="preserve">B-дерево, ключ поиска, план запроса, уникальность, стоимость обновления</t>
         </is>
       </c>
     </row>
     <row r="34" ht="45" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 24. Транзакции</t>
+        </is>
+      </c>
+      <c r="D34" s="6">
+        <v>2</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Разбираете транзакцию и свойства ACID: как COMMIT и ROLLBACK защищают данные и что происходит при сбое посреди операции.</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">транзакция, ACID, COMMIT, ROLLBACK, блокировка, сбой</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">32</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 21. Подзапросы</t>
-        </is>
-      </c>
-      <c r="D34" s="6">
-        <v>2</v>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Разбираете подзапросы в WHERE, FROM и SELECT: когда нужен скалярный результат, когда список значений и чем подзапрос отличается от JOIN.</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">подзапрос, скалярный подзапрос, IN, EXISTS, производная таблица</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="45" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33</t>
-        </is>
-      </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Лекция</t>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 22. Представления</t>
+          <t xml:space="preserve">Лекция 25. Импорт и экспорт JSON/CSV</t>
         </is>
       </c>
       <c r="D35" s="6">
@@ -1065,29 +1065,29 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете представления как сохранённый запрос: зачем они нужны, как скрывают структуру таблиц и когда представление нельзя обновлять.</t>
+          <t xml:space="preserve">Разбираете форматы JSON и CSV, сопоставление полей со столбцами и типичные ошибки кодировки и разделителей при переносе данных.</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREATE VIEW, представление, сохранённый запрос, обновляемость, права доступа</t>
+          <t xml:space="preserve">кодировка, разделитель, сопоставление полей, схема файла, потеря строк, заголовок столбцов</t>
         </is>
       </c>
     </row>
     <row r="36" ht="45" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 23. Индексы</t>
+          <t xml:space="preserve">Практика 6. Импорт JSON</t>
         </is>
       </c>
       <c r="D36" s="6">
@@ -1095,19 +1095,19 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете, как индекс ускоряет поиск, из чего он состоит и почему лишние индексы замедляют вставку и обновление.</t>
+          <t xml:space="preserve">Загружаете данные из JSON в таблицы учебной ИС, проверяете типы и полноту переноса и сдаёте скрипт импорта с отчётом о числе строк до и после.</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">B-дерево, ключ поиска, план запроса, уникальность, стоимость обновления</t>
+          <t xml:space="preserve">json-файл, сверка строк, типы данных, sqliteonline.com, скрипт загрузки</t>
         </is>
       </c>
     </row>
     <row r="37" ht="45" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 24. Транзакции</t>
+          <t xml:space="preserve">Лекция 26. Разграничение доступа</t>
         </is>
       </c>
       <c r="D37" s="6">
@@ -1125,42 +1125,42 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете транзакцию и свойства ACID: как COMMIT и ROLLBACK защищают данные и что происходит при сбое посреди операции.</t>
+          <t xml:space="preserve">Разбираете роли и права в базе: что дают SELECT, INSERT и DELETE, зачем нужен минимальный набор прав и как проверить выданные разрешения.</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">транзакция, ACID, COMMIT, ROLLBACK, блокировка, сбой</t>
+          <t xml:space="preserve">роль, GRANT, REVOKE, минимальные права, пользователь БД</t>
         </is>
       </c>
     </row>
     <row r="38" ht="60" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">35-36</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 25. Импорт и экспорт JSON/CSV</t>
+          <t xml:space="preserve">Практика 7. Индексы и транзакции; Разграничение доступа</t>
         </is>
       </c>
       <c r="D38" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете форматы JSON и CSV, сопоставление полей со столбцами и типичные ошибки кодировки и разделителей при переносе данных.</t>
+          <t xml:space="preserve">Сравниваете время запроса до и после создания индекса, проводите транзакцию с откатом и выдаёте роли разным пользователям, сдавая SQL-скрипт и замеры.</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">кодировка, разделитель, сопоставление полей, схема файла, потеря строк, заголовок столбцов</t>
+          <t xml:space="preserve">B-дерево, план запроса, транзакция, COMMIT, ROLLBACK, GRANT</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 26. Разграничение доступа</t>
+          <t xml:space="preserve">Лекция 27. Проектирование БД для ИС</t>
         </is>
       </c>
       <c r="D39" s="6">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбираете роли и права в базе: что дают SELECT, INSERT и DELETE, зачем нужен минимальный набор прав и как проверить выданные разрешения.</t>
+          <t xml:space="preserve">Собираете полный цикл проектирования: от требований и ER-модели до нормализации, ограничений и проверки запросами на реальных данных.</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">роль, GRANT, REVOKE, минимальные права, пользователь БД</t>
+          <t xml:space="preserve">требования, ER-модель, нормализация, ограничения, проверка запросами</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 27. Проектирование БД для ИС</t>
+          <t xml:space="preserve">Практика 8. Итоговая БД для учебной ИС</t>
         </is>
       </c>
       <c r="D40" s="6">
@@ -1215,12 +1215,12 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Собираете полный цикл проектирования: от требований и ER-модели до нормализации, ограничений и проверки запросами на реальных данных.</t>
+          <t xml:space="preserve">Собираете итоговую базу учебной ИС: ER-модель, таблицы с ограничениями, данные и типовые запросы, и сдаёте комплект из PDF-диаграммы и SQL-скрипта.</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">требования, ER-модель, нормализация, ограничения, проверка запросами</t>
+          <t xml:space="preserve">учебная ИС, схема БД, ER-модель, типовой запрос, комплект поставки</t>
         </is>
       </c>
     </row>
